--- a/results/543_z13/5_quantification/543_z13_quantification.xlsx
+++ b/results/543_z13/5_quantification/543_z13_quantification.xlsx
@@ -10,8 +10,9 @@
     <sheet name="per_image" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="width" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="per_lacuna" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="biological_limits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="per_lacuna" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,11 +447,6 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>n_bridges</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,9 +468,6 @@
       <c r="E2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
-        <v>19</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -706,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.7273</v>
+        <v>5.7273</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8316</v>
+        <v>1.954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -735,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>302.9091</v>
+        <v>274.0909</v>
       </c>
       <c r="D13" t="n">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="E13" t="n">
-        <v>50.1786</v>
+        <v>62.5083</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -764,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>961.3636</v>
+        <v>830.1818</v>
       </c>
       <c r="D14" t="n">
-        <v>944</v>
+        <v>819</v>
       </c>
       <c r="E14" t="n">
-        <v>107.7991</v>
+        <v>169.5328</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -793,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1713.9866</v>
+        <v>2254.9081</v>
       </c>
       <c r="D15" t="n">
-        <v>1167.8742</v>
+        <v>1814.6286</v>
       </c>
       <c r="E15" t="n">
-        <v>1503.6864</v>
+        <v>1416.8975</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -822,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>63.5455</v>
+        <v>95.63639999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="E16" t="n">
-        <v>56.0185</v>
+        <v>64.8047</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -851,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26.8926</v>
+        <v>25.017</v>
       </c>
       <c r="D17" t="n">
-        <v>27.1599</v>
+        <v>23.5144</v>
       </c>
       <c r="E17" t="n">
-        <v>4.8368</v>
+        <v>3.8232</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1025,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03624067</v>
+        <v>0.03303183</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03612809</v>
+        <v>0.03370953</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00540695</v>
+        <v>0.00792469</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1054,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04402843</v>
+        <v>0.03811779</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04358124</v>
+        <v>0.04085807</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00348523</v>
+        <v>0.00747877</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1083,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.2312</v>
+        <v>2.8038</v>
       </c>
       <c r="D25" t="n">
-        <v>3.5765</v>
+        <v>2.8301</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9956</v>
+        <v>0.8448</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1112,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>204.6364</v>
+        <v>205.4545</v>
       </c>
       <c r="D26" t="n">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="E26" t="n">
-        <v>75.6482</v>
+        <v>63.5537</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1141,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>498.3636</v>
+        <v>516.4545000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>412</v>
+        <v>507</v>
       </c>
       <c r="E27" t="n">
-        <v>253.3528</v>
+        <v>220.7824</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1170,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>341.9271</v>
+        <v>310.7516</v>
       </c>
       <c r="D28" t="n">
-        <v>347.6051</v>
+        <v>305.9483</v>
       </c>
       <c r="E28" t="n">
-        <v>60.217</v>
+        <v>70.378</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1199,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1087.2355</v>
+        <v>939.5478000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>1066.9626</v>
+        <v>925.9798</v>
       </c>
       <c r="E29" t="n">
-        <v>125.6712</v>
+        <v>193.4569</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1228,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8.0909</v>
+        <v>6.5455</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>2.7002</v>
+        <v>2.3394</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1257,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11.7273</v>
+        <v>10.0909</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>2.9014</v>
+        <v>2.8091</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1286,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14.2727</v>
+        <v>12.4545</v>
       </c>
       <c r="D32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>2.149</v>
+        <v>2.4234</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1315,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.9871</v>
+        <v>6.0179</v>
       </c>
       <c r="D33" t="n">
-        <v>5.0013</v>
+        <v>6.1511</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4355</v>
+        <v>0.4217</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1400,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>45033</v>
+        <v>36701</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1420,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04380241</v>
+        <v>0.0356981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1440,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>643</v>
+        <v>743</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1460,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00062543</v>
+        <v>0.0007226999999999999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1520,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>659</v>
+        <v>259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68.33540000000001</v>
+        <v>141.7027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04958231</v>
+        <v>0.04054955</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1600,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.04380241</v>
+        <v>0.0356981</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1673,7 +1666,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.7808</v>
+        <v>6.908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1693,7 +1686,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7.2111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1713,7 +1706,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.8284</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1733,7 +1726,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>8.9443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1753,7 +1746,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45013</v>
+        <v>36701</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1772,1285 +1765,407 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>lacuna_id</t>
+          <t>block</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>area_px2</t>
+          <t>item</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>major_axis_length_px</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>minor_axis_length_px</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>aspect_ratio</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>eccentricity</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>solidity</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>orientation_rad</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>centroid_row_px</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>centroid_col_px</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>on_border</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>roots_count</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ring_length_r30_px</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ring_length_r60_px</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>owned_length_px</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>edge_count</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>mean_edge_length_px</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>perimeter_px</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>ring_area_r30_px2</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>ring_area_r60_px2</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>in_frame_fraction_r30</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>in_frame_fraction_r60</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>ring_density_r30</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>ring_density_r60</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>roots_per_100px_perimeter</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>ring_attached_length_r30_px</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>ring_attached_length_r60_px</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ring_length_w_r30_px</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>ring_length_w_r60_px</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r10</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r20</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r30</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>ring_width_mean_r30_px</t>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>report only, nothing is pruned or filtered by this block</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>validated</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>along the network from the owning lacuna's surface to a thread end</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>range_um</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[25.0, 50.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>range_px_applied</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[192, 385]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>range_um_applied</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[24.96, 50.05]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>n_threads</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>median_um</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>25.2547</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>p10_um</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4.5441</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>p90_um</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>48.9438</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>max_um</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50.0487</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fraction_in_range</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5095</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fraction_below_range</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4905</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fraction_above_range</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>threads leaving the lacuna surface, interior lacunae only</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>n_lacunae</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2 x the distance transform of the mask at each sampled skeleton pixel</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>is_an_upper_bound</t>
+        </is>
+      </c>
+      <c r="C22" t="b">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C2" t="n">
-        <v>79.15349999999999</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33.2822</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.3783</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9073</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.9417</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.4378</v>
-      </c>
-      <c r="I2" t="n">
-        <v>97.9678</v>
-      </c>
-      <c r="J2" t="n">
-        <v>270.2858</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M2" t="n">
-        <v>331</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1011</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4094.9457</v>
-      </c>
-      <c r="P2" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>26.7644</v>
-      </c>
-      <c r="R2" t="n">
-        <v>205.0366</v>
-      </c>
-      <c r="S2" t="n">
-        <v>8499</v>
-      </c>
-      <c r="T2" t="n">
-        <v>22530</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.03894576</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.0448735</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>3.9017</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>278</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>651</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>391.7889</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1167.5849</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>4.8195</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>839</v>
-      </c>
-      <c r="C3" t="n">
-        <v>61.6665</v>
-      </c>
-      <c r="D3" t="n">
-        <v>17.863</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.4522</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9571</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.906</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="I3" t="n">
-        <v>131.3492</v>
-      </c>
-      <c r="J3" t="n">
-        <v>828.4386</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M3" t="n">
-        <v>310</v>
-      </c>
-      <c r="N3" t="n">
-        <v>883</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1843.9941</v>
-      </c>
-      <c r="P3" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>28.3691</v>
-      </c>
-      <c r="R3" t="n">
-        <v>151.2965</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6982</v>
-      </c>
-      <c r="T3" t="n">
-        <v>17707</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.04439989</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.04986728</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>4.6267</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>192</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>412</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>335.4508</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>979.1097</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>5.0013</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1736</v>
-      </c>
-      <c r="C4" t="n">
-        <v>73.3356</v>
-      </c>
-      <c r="D4" t="n">
-        <v>33.3815</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.1969</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8904</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.8374</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.2312</v>
-      </c>
-      <c r="I4" t="n">
-        <v>218.8203</v>
-      </c>
-      <c r="J4" t="n">
-        <v>919.2483</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M4" t="n">
-        <v>343</v>
-      </c>
-      <c r="N4" t="n">
-        <v>876</v>
-      </c>
-      <c r="O4" t="n">
-        <v>915.0092</v>
-      </c>
-      <c r="P4" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>27.7276</v>
-      </c>
-      <c r="R4" t="n">
-        <v>205.0366</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8219</v>
-      </c>
-      <c r="T4" t="n">
-        <v>20045</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.04173257</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.04370167</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>4.3895</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>218</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>388</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>388.8478</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>986.9626</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.6128</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1138</v>
-      </c>
-      <c r="C5" t="n">
-        <v>46.8317</v>
-      </c>
-      <c r="D5" t="n">
-        <v>31.6227</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.481</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.7376</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.9252</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="I5" t="n">
-        <v>263.1037</v>
-      </c>
-      <c r="J5" t="n">
-        <v>340.4982</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>226</v>
-      </c>
-      <c r="N5" t="n">
-        <v>828</v>
-      </c>
-      <c r="O5" t="n">
-        <v>515.6884</v>
-      </c>
-      <c r="P5" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>36.8349</v>
-      </c>
-      <c r="R5" t="n">
-        <v>139.6812</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6734</v>
-      </c>
-      <c r="T5" t="n">
-        <v>18999</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.03356103</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.04358124</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.1477</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>286</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>259.0366</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>938.1219</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>5.2431</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2267</v>
-      </c>
-      <c r="C6" t="n">
-        <v>87.9083</v>
-      </c>
-      <c r="D6" t="n">
-        <v>33.2852</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2.6411</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.9255</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.9473</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0042</v>
-      </c>
-      <c r="I6" t="n">
-        <v>459.6211</v>
-      </c>
-      <c r="J6" t="n">
-        <v>481.0926</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>326</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1067</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4189.1934</v>
-      </c>
-      <c r="P6" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>27.928</v>
-      </c>
-      <c r="R6" t="n">
-        <v>223.8234</v>
-      </c>
-      <c r="S6" t="n">
-        <v>8900</v>
-      </c>
-      <c r="T6" t="n">
-        <v>23453</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.03662921</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.04549525</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.2339</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>161</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>696</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>364.9066</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1191.4062</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>5.4269</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>860</v>
-      </c>
-      <c r="C7" t="n">
-        <v>45.4745</v>
-      </c>
-      <c r="D7" t="n">
-        <v>26.4762</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.7176</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.8129999999999999</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.854</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>475.2209</v>
-      </c>
-      <c r="J7" t="n">
-        <v>748.086</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>287</v>
-      </c>
-      <c r="N7" t="n">
-        <v>861</v>
-      </c>
-      <c r="O7" t="n">
-        <v>284.9361</v>
-      </c>
-      <c r="P7" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>17.8085</v>
-      </c>
-      <c r="R7" t="n">
-        <v>141.3381</v>
-      </c>
-      <c r="S7" t="n">
-        <v>6516</v>
-      </c>
-      <c r="T7" t="n">
-        <v>17817</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.04404543</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.04832463</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.8301</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>189</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>271</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>327.0782</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>977.4356</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>4.8186</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2150</v>
-      </c>
-      <c r="C8" t="n">
-        <v>103.9176</v>
-      </c>
-      <c r="D8" t="n">
-        <v>27.5311</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3.7745</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.9643</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.9231</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.2711</v>
-      </c>
-      <c r="I8" t="n">
-        <v>546.6735</v>
-      </c>
-      <c r="J8" t="n">
-        <v>873.7344000000001</v>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>308</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1041</v>
-      </c>
-      <c r="O8" t="n">
-        <v>167.5807</v>
-      </c>
-      <c r="P8" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>20.9476</v>
-      </c>
-      <c r="R8" t="n">
-        <v>254.9361</v>
-      </c>
-      <c r="S8" t="n">
-        <v>9810</v>
-      </c>
-      <c r="T8" t="n">
-        <v>24446</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.03139653</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.04258365</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.569</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>139</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>252</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>347.6051</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1176.6438</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>4.347</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3069</v>
-      </c>
-      <c r="C9" t="n">
-        <v>109.3585</v>
-      </c>
-      <c r="D9" t="n">
-        <v>37.084</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.9489</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9407</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.9099</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="I9" t="n">
-        <v>642.6703</v>
-      </c>
-      <c r="J9" t="n">
-        <v>188.3297</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
-        <v>317</v>
-      </c>
-      <c r="N9" t="n">
-        <v>955</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1859.2977</v>
-      </c>
-      <c r="P9" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>26.9463</v>
-      </c>
-      <c r="R9" t="n">
-        <v>278.5929</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10387</v>
-      </c>
-      <c r="T9" t="n">
-        <v>26403</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.03051892</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.03617013</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>3.5895</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>282</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>748</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>362.8772</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1095.1585</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>5.3506</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1616</v>
-      </c>
-      <c r="C10" t="n">
-        <v>74.0218</v>
-      </c>
-      <c r="D10" t="n">
-        <v>28.3763</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2.6086</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.9236</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.9245</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.0477</v>
-      </c>
-      <c r="I10" t="n">
-        <v>731.5359</v>
-      </c>
-      <c r="J10" t="n">
-        <v>630.2376</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" t="n">
-        <v>254</v>
-      </c>
-      <c r="N10" t="n">
-        <v>944</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1167.8742</v>
-      </c>
-      <c r="P10" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>27.1599</v>
-      </c>
-      <c r="R10" t="n">
-        <v>195.7229</v>
-      </c>
-      <c r="S10" t="n">
-        <v>8083</v>
-      </c>
-      <c r="T10" t="n">
-        <v>21794</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.03142398</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.04331467</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>3.5765</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>220</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>664</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>282.8944</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1066.9626</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>5.0347</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1438</v>
-      </c>
-      <c r="C11" t="n">
-        <v>72.50920000000001</v>
-      </c>
-      <c r="D11" t="n">
-        <v>25.5367</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.8394</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.9359</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.9236</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0953</v>
-      </c>
-      <c r="I11" t="n">
-        <v>793.1369999999999</v>
-      </c>
-      <c r="J11" t="n">
-        <v>478.379</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>234</v>
-      </c>
-      <c r="N11" t="n">
-        <v>918</v>
-      </c>
-      <c r="O11" t="n">
-        <v>511.9605</v>
-      </c>
-      <c r="P11" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>30.1153</v>
-      </c>
-      <c r="R11" t="n">
-        <v>184.9949</v>
-      </c>
-      <c r="S11" t="n">
-        <v>7835</v>
-      </c>
-      <c r="T11" t="n">
-        <v>21305</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.02986599</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.04308848</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.7028</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>102</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>166</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>250.8234</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1024.3351</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>4.4422</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>3350</v>
-      </c>
-      <c r="C12" t="n">
-        <v>107.7995</v>
-      </c>
-      <c r="D12" t="n">
-        <v>44.5116</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.4218</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.9108000000000001</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.8475</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.08799999999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>854.9167</v>
-      </c>
-      <c r="J12" t="n">
-        <v>288.1039</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M12" t="n">
-        <v>396</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1191</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3303.3729</v>
-      </c>
-      <c r="P12" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>25.2166</v>
-      </c>
-      <c r="R12" t="n">
-        <v>301.8061</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10961</v>
-      </c>
-      <c r="T12" t="n">
-        <v>27498</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.03612809</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.04331224</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>3.9761</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>350</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>948</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>449.8894</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1355.8692</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>5.7617</v>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>it includes the optical blur, which widens a thread beyond its true size, and no point spread function is subtracted: the numerical aperture, the emission wavelength and the pinhole are unknown. It is an apparent width in the image, not a canalicular diameter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>median_um</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9374</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>p10_um</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>p90_um</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.1628</v>
       </c>
     </row>
   </sheetData>
@@ -3064,6 +2179,1298 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AG12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lacuna_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>area_px2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>major_axis_length_px</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minor_axis_length_px</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aspect_ratio</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eccentricity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>solidity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>orientation_rad</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>centroid_row_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>centroid_col_px</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>on_border</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>roots_count</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ring_length_r30_px</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ring_length_r60_px</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>owned_length_px</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mean_edge_length_px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ring_width_mean_r30_px</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C2" t="n">
+        <v>79.15349999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33.2822</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.3783</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9073</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9417</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="I2" t="n">
+        <v>97.9678</v>
+      </c>
+      <c r="J2" t="n">
+        <v>270.2858</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>256</v>
+      </c>
+      <c r="N2" t="n">
+        <v>764</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3223.042</v>
+      </c>
+      <c r="P2" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>22.2279</v>
+      </c>
+      <c r="R2" t="n">
+        <v>205.0366</v>
+      </c>
+      <c r="S2" t="n">
+        <v>8499</v>
+      </c>
+      <c r="T2" t="n">
+        <v>22530</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.03012119</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.03391034</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.9263</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>235</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>520</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>305.9483</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>881.7494</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>6.3462</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>839</v>
+      </c>
+      <c r="C3" t="n">
+        <v>61.6665</v>
+      </c>
+      <c r="D3" t="n">
+        <v>17.863</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.4522</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9571</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="I3" t="n">
+        <v>131.3492</v>
+      </c>
+      <c r="J3" t="n">
+        <v>828.4386</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>281</v>
+      </c>
+      <c r="N3" t="n">
+        <v>693</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3091.9983</v>
+      </c>
+      <c r="P3" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>25.7667</v>
+      </c>
+      <c r="R3" t="n">
+        <v>151.2965</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6982</v>
+      </c>
+      <c r="T3" t="n">
+        <v>17707</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.04024635</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.03913706</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.3048</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>238</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>507</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>304.9239</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>755.86</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5.7936</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1736</v>
+      </c>
+      <c r="C4" t="n">
+        <v>73.3356</v>
+      </c>
+      <c r="D4" t="n">
+        <v>33.3815</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.1969</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8904</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8374</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2312</v>
+      </c>
+      <c r="I4" t="n">
+        <v>218.8203</v>
+      </c>
+      <c r="J4" t="n">
+        <v>919.2483</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>310</v>
+      </c>
+      <c r="N4" t="n">
+        <v>819</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1726.19</v>
+      </c>
+      <c r="P4" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>24.3125</v>
+      </c>
+      <c r="R4" t="n">
+        <v>205.0366</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8219</v>
+      </c>
+      <c r="T4" t="n">
+        <v>20045</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.03771748</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.04085807</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.3895</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>210</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>510</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>351.6346</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>925.9798</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>5.655</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1138</v>
+      </c>
+      <c r="C5" t="n">
+        <v>46.8317</v>
+      </c>
+      <c r="D5" t="n">
+        <v>31.6227</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7376</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9252</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="I5" t="n">
+        <v>263.1037</v>
+      </c>
+      <c r="J5" t="n">
+        <v>340.4982</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>227</v>
+      </c>
+      <c r="N5" t="n">
+        <v>855</v>
+      </c>
+      <c r="O5" t="n">
+        <v>866.6072</v>
+      </c>
+      <c r="P5" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>22.8055</v>
+      </c>
+      <c r="R5" t="n">
+        <v>139.6812</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6734</v>
+      </c>
+      <c r="T5" t="n">
+        <v>18999</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.03370953</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.04500237</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.1477</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>128</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>261.2082</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>964.9087</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>6.1511</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2267</v>
+      </c>
+      <c r="C6" t="n">
+        <v>87.9083</v>
+      </c>
+      <c r="D6" t="n">
+        <v>33.2852</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.6411</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9255</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9473</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="I6" t="n">
+        <v>459.6211</v>
+      </c>
+      <c r="J6" t="n">
+        <v>481.0926</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>326</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1012</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3937.2157</v>
+      </c>
+      <c r="P6" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>23.1601</v>
+      </c>
+      <c r="R6" t="n">
+        <v>223.8234</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8900</v>
+      </c>
+      <c r="T6" t="n">
+        <v>23453</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.03662921</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.04315013</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.1275</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>219</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>652</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>369.0488</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1139.7494</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>6.2124</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>860</v>
+      </c>
+      <c r="C7" t="n">
+        <v>45.4745</v>
+      </c>
+      <c r="D7" t="n">
+        <v>26.4762</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.7176</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>475.2209</v>
+      </c>
+      <c r="J7" t="n">
+        <v>748.086</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>310</v>
+      </c>
+      <c r="N7" t="n">
+        <v>889</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2774.7018</v>
+      </c>
+      <c r="P7" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23.5144</v>
+      </c>
+      <c r="R7" t="n">
+        <v>141.3381</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6516</v>
+      </c>
+      <c r="T7" t="n">
+        <v>17817</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.0475752</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.04989617</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.8301</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>268</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>683</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>345.2792</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1004.5656</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>5.9959</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2150</v>
+      </c>
+      <c r="C8" t="n">
+        <v>103.9176</v>
+      </c>
+      <c r="D8" t="n">
+        <v>27.5311</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.7745</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="I8" t="n">
+        <v>546.6735</v>
+      </c>
+      <c r="J8" t="n">
+        <v>873.7344000000001</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>293</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1005</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1177.8032</v>
+      </c>
+      <c r="P8" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>23.5561</v>
+      </c>
+      <c r="R8" t="n">
+        <v>254.9361</v>
+      </c>
+      <c r="S8" t="n">
+        <v>9810</v>
+      </c>
+      <c r="T8" t="n">
+        <v>24446</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.02986748</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.04111102</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.3535</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>188</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>331.5635</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1138.0753</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>5.418</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3069</v>
+      </c>
+      <c r="C9" t="n">
+        <v>109.3585</v>
+      </c>
+      <c r="D9" t="n">
+        <v>37.084</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.9489</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9407</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9099</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="I9" t="n">
+        <v>642.6703</v>
+      </c>
+      <c r="J9" t="n">
+        <v>188.3297</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>205</v>
+      </c>
+      <c r="N9" t="n">
+        <v>705</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1814.6286</v>
+      </c>
+      <c r="P9" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="R9" t="n">
+        <v>278.5929</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10387</v>
+      </c>
+      <c r="T9" t="n">
+        <v>26403</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.01973621</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.02670151</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.7947</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>162</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>494</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>240.865</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>815.3229</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>6.3804</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1616</v>
+      </c>
+      <c r="C10" t="n">
+        <v>74.0218</v>
+      </c>
+      <c r="D10" t="n">
+        <v>28.3763</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.6086</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9236</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9245</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.0477</v>
+      </c>
+      <c r="I10" t="n">
+        <v>731.5359</v>
+      </c>
+      <c r="J10" t="n">
+        <v>630.2376</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>186</v>
+      </c>
+      <c r="N10" t="n">
+        <v>590</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1091.6488</v>
+      </c>
+      <c r="P10" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>33.0803</v>
+      </c>
+      <c r="R10" t="n">
+        <v>195.7229</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8083</v>
+      </c>
+      <c r="T10" t="n">
+        <v>21794</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.02301126</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.02707167</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.5328</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>112</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>338</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>207.9533</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>671.4996</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6.2749</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1438</v>
+      </c>
+      <c r="C11" t="n">
+        <v>72.50920000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>25.5367</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.8394</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9359</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9236</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0953</v>
+      </c>
+      <c r="I11" t="n">
+        <v>793.1369999999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>478.379</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>222</v>
+      </c>
+      <c r="N11" t="n">
+        <v>662</v>
+      </c>
+      <c r="O11" t="n">
+        <v>286.3087</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>31.8121</v>
+      </c>
+      <c r="R11" t="n">
+        <v>184.9949</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7835</v>
+      </c>
+      <c r="T11" t="n">
+        <v>21305</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.0283344</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.03107252</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.7839</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>168</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>263</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>245.5097</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>742.2275</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>5.3237</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3350</v>
+      </c>
+      <c r="C12" t="n">
+        <v>107.7995</v>
+      </c>
+      <c r="D12" t="n">
+        <v>44.5116</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.4218</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8475</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.08799999999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>854.9167</v>
+      </c>
+      <c r="J12" t="n">
+        <v>288.1039</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>399</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1138</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4813.8452</v>
+      </c>
+      <c r="P12" t="n">
+        <v>219</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>21.981</v>
+      </c>
+      <c r="R12" t="n">
+        <v>301.8061</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10961</v>
+      </c>
+      <c r="T12" t="n">
+        <v>27498</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.03640179</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.04138483</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.6507</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>332</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1044</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>454.333</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1295.0874</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>6.6452</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3084,7 +3491,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Measured only on skeleton pixels with real signal under them: bridged pixels, the lacuna buffer and the</t>
+          <t>Measured only on skeleton pixels on the canalicular mask: the lacuna buffer and the</t>
         </is>
       </c>
     </row>

--- a/results/543_z13/5_quantification/543_z13_quantification.xlsx
+++ b/results/543_z13/5_quantification/543_z13_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.7273</v>
+        <v>4.3636</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>1.954</v>
+        <v>2.1574</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>274.0909</v>
+        <v>310.3636</v>
       </c>
       <c r="D13" t="n">
-        <v>281</v>
+        <v>331</v>
       </c>
       <c r="E13" t="n">
-        <v>62.5083</v>
+        <v>59.7533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>830.1818</v>
+        <v>922.8182</v>
       </c>
       <c r="D14" t="n">
-        <v>819</v>
+        <v>912</v>
       </c>
       <c r="E14" t="n">
-        <v>169.5328</v>
+        <v>141.2854</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2254.9081</v>
+        <v>2884.7218</v>
       </c>
       <c r="D15" t="n">
-        <v>1814.6286</v>
+        <v>2192.3221</v>
       </c>
       <c r="E15" t="n">
-        <v>1416.8975</v>
+        <v>1747.8175</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>95.63639999999999</v>
+        <v>126.7273</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E16" t="n">
-        <v>64.8047</v>
+        <v>83.8357</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.017</v>
+        <v>24.3069</v>
       </c>
       <c r="D17" t="n">
-        <v>23.5144</v>
+        <v>22.7652</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8232</v>
+        <v>3.6281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03303183</v>
+        <v>0.03743945</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03370953</v>
+        <v>0.03534304</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00792469</v>
+        <v>0.008597459999999999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03811779</v>
+        <v>0.042466</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04085807</v>
+        <v>0.04349407</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00747877</v>
+        <v>0.00710373</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.8038</v>
+        <v>2.1027</v>
       </c>
       <c r="D25" t="n">
-        <v>2.8301</v>
+        <v>2.1226</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8448</v>
+        <v>0.8621</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>205.4545</v>
+        <v>244.9091</v>
       </c>
       <c r="D26" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="E26" t="n">
-        <v>63.5537</v>
+        <v>60.881</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>516.4545000000001</v>
+        <v>657.9091</v>
       </c>
       <c r="D27" t="n">
-        <v>507</v>
+        <v>740</v>
       </c>
       <c r="E27" t="n">
-        <v>220.7824</v>
+        <v>203.508</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>310.7516</v>
+        <v>352.2418</v>
       </c>
       <c r="D28" t="n">
-        <v>305.9483</v>
+        <v>376.5341</v>
       </c>
       <c r="E28" t="n">
-        <v>70.378</v>
+        <v>66.4289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>939.5478000000001</v>
+        <v>1046.4873</v>
       </c>
       <c r="D29" t="n">
-        <v>925.9798</v>
+        <v>1055.0092</v>
       </c>
       <c r="E29" t="n">
-        <v>193.4569</v>
+        <v>158.4975</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.5455</v>
+        <v>6.8182</v>
       </c>
       <c r="D30" t="n">
         <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>2.3394</v>
+        <v>2.2724</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10.0909</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>2.8091</v>
+        <v>2.7203</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12.4545</v>
+        <v>13.4545</v>
       </c>
       <c r="D32" t="n">
         <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>2.4234</v>
+        <v>2.1616</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.0179</v>
+        <v>7.0667</v>
       </c>
       <c r="D33" t="n">
-        <v>6.1511</v>
+        <v>7.3794</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4217</v>
+        <v>0.6515</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36701</v>
+        <v>41364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0356981</v>
+        <v>0.04023368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>743</v>
+        <v>926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0007226999999999999</v>
+        <v>0.0009007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>141.7027</v>
+        <v>179.0649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04054955</v>
+        <v>0.04570415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0356981</v>
+        <v>0.04023368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,6 +1613,86 @@
         </is>
       </c>
       <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>unattached_length_px</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>256</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>unattached_component_count</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_attached_per_px</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.04023368</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>field_length_density_with_unattached_per_px</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.04048268</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
         </is>
@@ -1666,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.908</v>
+        <v>7.6176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1686,7 +1766,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.2111</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1706,7 +1786,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>4.4721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1726,7 +1806,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.9443</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1746,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36701</v>
+        <v>41364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1889,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>528</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9">
@@ -1904,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25.2547</v>
+        <v>24.2016</v>
       </c>
     </row>
     <row r="10">
@@ -1919,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.5441</v>
+        <v>4.4396</v>
       </c>
     </row>
     <row r="11">
@@ -1934,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>48.9438</v>
+        <v>47.1468</v>
       </c>
     </row>
     <row r="12">
@@ -1964,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5095</v>
+        <v>0.4762</v>
       </c>
     </row>
     <row r="14">
@@ -1979,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4905</v>
+        <v>0.5238</v>
       </c>
     </row>
     <row r="15">
@@ -2041,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -2056,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2071,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -2135,7 +2215,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9374</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="25">
@@ -2150,7 +2230,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.52</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="26">
@@ -2165,7 +2245,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.1628</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -2384,22 +2464,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="N2" t="n">
-        <v>764</v>
+        <v>912</v>
       </c>
       <c r="O2" t="n">
-        <v>3223.042</v>
+        <v>3742.8187</v>
       </c>
       <c r="P2" t="n">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.2279</v>
+        <v>21.7606</v>
       </c>
       <c r="R2" t="n">
         <v>205.0366</v>
@@ -2417,37 +2497,37 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03012119</v>
+        <v>0.03470997</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03391034</v>
+        <v>0.04047936</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.9263</v>
+        <v>2.4386</v>
       </c>
       <c r="Z2" t="n">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="AA2" t="n">
-        <v>520</v>
+        <v>826</v>
       </c>
       <c r="AB2" t="n">
-        <v>305.9483</v>
+        <v>353.8894</v>
       </c>
       <c r="AC2" t="n">
-        <v>881.7494</v>
+        <v>1057.0458</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="n">
         <v>10</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.3462</v>
+        <v>7.4007</v>
       </c>
     </row>
     <row r="3">
@@ -2485,22 +2565,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>281</v>
+        <v>354</v>
       </c>
       <c r="N3" t="n">
-        <v>693</v>
+        <v>951</v>
       </c>
       <c r="O3" t="n">
-        <v>3091.9983</v>
+        <v>4644.1101</v>
       </c>
       <c r="P3" t="n">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.7667</v>
+        <v>22.7652</v>
       </c>
       <c r="R3" t="n">
         <v>151.2965</v>
@@ -2518,37 +2598,37 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.04024635</v>
+        <v>0.0507018</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03913706</v>
+        <v>0.05370757</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.3048</v>
+        <v>2.6438</v>
       </c>
       <c r="Z3" t="n">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="AA3" t="n">
-        <v>507</v>
+        <v>740</v>
       </c>
       <c r="AB3" t="n">
-        <v>304.9239</v>
+        <v>391.2792</v>
       </c>
       <c r="AC3" t="n">
-        <v>755.86</v>
+        <v>1062.2813</v>
       </c>
       <c r="AD3" t="n">
         <v>6</v>
       </c>
       <c r="AE3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.7936</v>
+        <v>6.6482</v>
       </c>
     </row>
     <row r="4">
@@ -2586,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="N4" t="n">
-        <v>819</v>
+        <v>876</v>
       </c>
       <c r="O4" t="n">
-        <v>1726.19</v>
+        <v>1524.5971</v>
       </c>
       <c r="P4" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.3125</v>
+        <v>24.5903</v>
       </c>
       <c r="R4" t="n">
         <v>205.0366</v>
@@ -2619,37 +2699,37 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03771748</v>
+        <v>0.04027254</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04085807</v>
+        <v>0.04370167</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.3895</v>
+        <v>3.9017</v>
       </c>
       <c r="Z4" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="AA4" t="n">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="AB4" t="n">
-        <v>351.6346</v>
+        <v>376.5341</v>
       </c>
       <c r="AC4" t="n">
-        <v>925.9798</v>
+        <v>993.7494</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF4" t="n">
         <v>12</v>
       </c>
-      <c r="AF4" t="n">
-        <v>13</v>
-      </c>
       <c r="AG4" t="n">
-        <v>5.655</v>
+        <v>6.4844</v>
       </c>
     </row>
     <row r="5">
@@ -2687,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="N5" t="n">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="O5" t="n">
-        <v>866.6072</v>
+        <v>1293.3006</v>
       </c>
       <c r="P5" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.8055</v>
+        <v>24.8712</v>
       </c>
       <c r="R5" t="n">
         <v>139.6812</v>
@@ -2720,28 +2800,28 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03370953</v>
+        <v>0.03534304</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04500237</v>
+        <v>0.04516027</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.1477</v>
+        <v>1.4318</v>
       </c>
       <c r="Z5" t="n">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="AA5" t="n">
-        <v>320</v>
+        <v>460</v>
       </c>
       <c r="AB5" t="n">
-        <v>261.2082</v>
+        <v>276.1076</v>
       </c>
       <c r="AC5" t="n">
-        <v>964.9087</v>
+        <v>972.1514</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>8</v>
@@ -2750,7 +2830,7 @@
         <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.1511</v>
+        <v>7.7768</v>
       </c>
     </row>
     <row r="6">
@@ -2788,22 +2868,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="N6" t="n">
-        <v>1012</v>
+        <v>1047</v>
       </c>
       <c r="O6" t="n">
-        <v>3937.2157</v>
+        <v>5504.2737</v>
       </c>
       <c r="P6" t="n">
-        <v>170</v>
+        <v>247</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.1601</v>
+        <v>22.2845</v>
       </c>
       <c r="R6" t="n">
         <v>223.8234</v>
@@ -2821,25 +2901,25 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03662921</v>
+        <v>0.03898876</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04315013</v>
+        <v>0.04464248</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.1275</v>
+        <v>2.6807</v>
       </c>
       <c r="Z6" t="n">
-        <v>219</v>
+        <v>286</v>
       </c>
       <c r="AA6" t="n">
-        <v>652</v>
+        <v>784</v>
       </c>
       <c r="AB6" t="n">
-        <v>369.0488</v>
+        <v>389.3209</v>
       </c>
       <c r="AC6" t="n">
-        <v>1139.7494</v>
+        <v>1168.3646</v>
       </c>
       <c r="AD6" t="n">
         <v>7</v>
@@ -2851,7 +2931,7 @@
         <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.2124</v>
+        <v>7.8264</v>
       </c>
     </row>
     <row r="7">
@@ -2889,22 +2969,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>310</v>
+        <v>353</v>
       </c>
       <c r="N7" t="n">
-        <v>889</v>
+        <v>942</v>
       </c>
       <c r="O7" t="n">
-        <v>2774.7018</v>
+        <v>2173.9302</v>
       </c>
       <c r="P7" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="Q7" t="n">
-        <v>23.5144</v>
+        <v>20.3171</v>
       </c>
       <c r="R7" t="n">
         <v>141.3381</v>
@@ -2922,37 +3002,37 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0475752</v>
+        <v>0.05417434</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04989617</v>
+        <v>0.05287085</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.8301</v>
+        <v>2.1226</v>
       </c>
       <c r="Z7" t="n">
-        <v>268</v>
+        <v>310</v>
       </c>
       <c r="AA7" t="n">
-        <v>683</v>
+        <v>760</v>
       </c>
       <c r="AB7" t="n">
-        <v>345.2792</v>
+        <v>392.5219</v>
       </c>
       <c r="AC7" t="n">
-        <v>1004.5656</v>
+        <v>1055.0092</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.9959</v>
+        <v>7.3794</v>
       </c>
     </row>
     <row r="8">
@@ -2990,22 +3070,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="N8" t="n">
-        <v>1005</v>
+        <v>1052</v>
       </c>
       <c r="O8" t="n">
-        <v>1177.8032</v>
+        <v>2914.0033</v>
       </c>
       <c r="P8" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="Q8" t="n">
-        <v>23.5561</v>
+        <v>22.4154</v>
       </c>
       <c r="R8" t="n">
         <v>254.9361</v>
@@ -3023,37 +3103,37 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02986748</v>
+        <v>0.0343527</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04111102</v>
+        <v>0.04303363</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3535</v>
+        <v>1.569</v>
       </c>
       <c r="Z8" t="n">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="AA8" t="n">
-        <v>350</v>
+        <v>503</v>
       </c>
       <c r="AB8" t="n">
-        <v>331.5635</v>
+        <v>380.463</v>
       </c>
       <c r="AC8" t="n">
-        <v>1138.0753</v>
+        <v>1188.9747</v>
       </c>
       <c r="AD8" t="n">
         <v>7</v>
       </c>
       <c r="AE8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF8" t="n">
         <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.418</v>
+        <v>6.3621</v>
       </c>
     </row>
     <row r="9">
@@ -3091,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>205</v>
+        <v>274</v>
       </c>
       <c r="N9" t="n">
-        <v>705</v>
+        <v>875</v>
       </c>
       <c r="O9" t="n">
-        <v>1814.6286</v>
+        <v>2192.3221</v>
       </c>
       <c r="P9" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.97</v>
+        <v>25.1991</v>
       </c>
       <c r="R9" t="n">
         <v>278.5929</v>
@@ -3124,37 +3204,37 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01973621</v>
+        <v>0.02637913</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02670151</v>
+        <v>0.03314017</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.7947</v>
+        <v>1.0768</v>
       </c>
       <c r="Z9" t="n">
-        <v>162</v>
+        <v>228</v>
       </c>
       <c r="AA9" t="n">
-        <v>494</v>
+        <v>855</v>
       </c>
       <c r="AB9" t="n">
-        <v>240.865</v>
+        <v>315.9066</v>
       </c>
       <c r="AC9" t="n">
-        <v>815.3229</v>
+        <v>1017.4184</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.3804</v>
+        <v>7.4497</v>
       </c>
     </row>
     <row r="10">
@@ -3195,19 +3275,19 @@
         <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>186</v>
+        <v>230</v>
       </c>
       <c r="N10" t="n">
-        <v>590</v>
+        <v>748</v>
       </c>
       <c r="O10" t="n">
-        <v>1091.6488</v>
+        <v>1612.1951</v>
       </c>
       <c r="P10" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Q10" t="n">
-        <v>33.0803</v>
+        <v>30.4188</v>
       </c>
       <c r="R10" t="n">
         <v>195.7229</v>
@@ -3225,37 +3305,37 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02301126</v>
+        <v>0.02845478</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02707167</v>
+        <v>0.03432137</v>
       </c>
       <c r="Y10" t="n">
         <v>1.5328</v>
       </c>
       <c r="Z10" t="n">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="AA10" t="n">
-        <v>338</v>
+        <v>496</v>
       </c>
       <c r="AB10" t="n">
-        <v>207.9533</v>
+        <v>260.6518</v>
       </c>
       <c r="AC10" t="n">
-        <v>671.4996</v>
+        <v>856.8377</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.2749</v>
+        <v>6.815</v>
       </c>
     </row>
     <row r="11">
@@ -3293,22 +3373,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="N11" t="n">
-        <v>662</v>
+        <v>694</v>
       </c>
       <c r="O11" t="n">
-        <v>286.3087</v>
+        <v>535.1442</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.8121</v>
+        <v>31.4791</v>
       </c>
       <c r="R11" t="n">
         <v>184.9949</v>
@@ -3326,25 +3406,25 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0283344</v>
+        <v>0.03050415</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03107252</v>
+        <v>0.03257451</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.7839</v>
+        <v>1.0811</v>
       </c>
       <c r="Z11" t="n">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="AA11" t="n">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="AB11" t="n">
-        <v>245.5097</v>
+        <v>263.7523</v>
       </c>
       <c r="AC11" t="n">
-        <v>742.2275</v>
+        <v>778.7128</v>
       </c>
       <c r="AD11" t="n">
         <v>5</v>
@@ -3356,7 +3436,7 @@
         <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>5.3237</v>
+        <v>5.9049</v>
       </c>
     </row>
     <row r="12">
@@ -3397,19 +3477,19 @@
         <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="N12" t="n">
-        <v>1138</v>
+        <v>1196</v>
       </c>
       <c r="O12" t="n">
-        <v>4813.8452</v>
+        <v>5595.2442</v>
       </c>
       <c r="P12" t="n">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.981</v>
+        <v>21.2747</v>
       </c>
       <c r="R12" t="n">
         <v>301.8061</v>
@@ -3427,37 +3507,37 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03640179</v>
+        <v>0.03795274</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04138483</v>
+        <v>0.04349407</v>
       </c>
       <c r="Y12" t="n">
         <v>2.6507</v>
       </c>
       <c r="Z12" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AA12" t="n">
-        <v>1044</v>
+        <v>966</v>
       </c>
       <c r="AB12" t="n">
-        <v>454.333</v>
+        <v>474.2325</v>
       </c>
       <c r="AC12" t="n">
-        <v>1295.0874</v>
+        <v>1360.8154</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF12" t="n">
         <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.6452</v>
+        <v>7.6863</v>
       </c>
     </row>
   </sheetData>

--- a/results/543_z13/5_quantification/543_z13_quantification.xlsx
+++ b/results/543_z13/5_quantification/543_z13_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.3636</v>
+        <v>6.3636</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1574</v>
+        <v>2.2923</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>310.3636</v>
+        <v>311</v>
       </c>
       <c r="D13" t="n">
         <v>331</v>
       </c>
       <c r="E13" t="n">
-        <v>59.7533</v>
+        <v>58.9016</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>922.8182</v>
+        <v>923.7273</v>
       </c>
       <c r="D14" t="n">
         <v>912</v>
       </c>
       <c r="E14" t="n">
-        <v>141.2854</v>
+        <v>139.5049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2884.7218</v>
+        <v>2910.1134</v>
       </c>
       <c r="D15" t="n">
-        <v>2192.3221</v>
+        <v>2471.8734</v>
       </c>
       <c r="E15" t="n">
-        <v>1747.8175</v>
+        <v>1677.5872</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>126.7273</v>
+        <v>127.4545</v>
       </c>
       <c r="D16" t="n">
         <v>107</v>
       </c>
       <c r="E16" t="n">
-        <v>83.8357</v>
+        <v>81.1669</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.3069</v>
+        <v>24.4052</v>
       </c>
       <c r="D17" t="n">
-        <v>22.7652</v>
+        <v>22.6631</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6281</v>
+        <v>3.8624</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03743945</v>
+        <v>0.03751996</v>
       </c>
       <c r="D23" t="n">
         <v>0.03534304</v>
       </c>
       <c r="E23" t="n">
-        <v>0.008597459999999999</v>
+        <v>0.008522099999999999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.042466</v>
+        <v>0.04250902</v>
       </c>
       <c r="D24" t="n">
         <v>0.04349407</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00710373</v>
+        <v>0.00703491</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.1027</v>
+        <v>3.113</v>
       </c>
       <c r="D25" t="n">
-        <v>2.1226</v>
+        <v>3.2433</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8621</v>
+        <v>0.901</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>244.9091</v>
+        <v>245.5455</v>
       </c>
       <c r="D26" t="n">
         <v>260</v>
       </c>
       <c r="E26" t="n">
-        <v>60.881</v>
+        <v>60.0889</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>657.9091</v>
+        <v>658.8182</v>
       </c>
       <c r="D27" t="n">
         <v>740</v>
       </c>
       <c r="E27" t="n">
-        <v>203.508</v>
+        <v>201.9613</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>352.2418</v>
+        <v>352.9911</v>
       </c>
       <c r="D28" t="n">
         <v>376.5341</v>
       </c>
       <c r="E28" t="n">
-        <v>66.4289</v>
+        <v>65.16759999999999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1046.4873</v>
+        <v>1047.5094</v>
       </c>
       <c r="D29" t="n">
         <v>1055.0092</v>
       </c>
       <c r="E29" t="n">
-        <v>158.4975</v>
+        <v>156.4744</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>11.0909</v>
       </c>
       <c r="D31" t="n">
         <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>2.7203</v>
+        <v>2.5477</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.0667</v>
+        <v>7.1679</v>
       </c>
       <c r="D33" t="n">
         <v>7.3794</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6515</v>
+        <v>0.5203</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41364</v>
+        <v>41377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04023368</v>
+        <v>0.04024632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>179.0649</v>
+        <v>179.1212</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04570415</v>
+        <v>0.045718</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.04023368</v>
+        <v>0.04024632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.04023368</v>
+        <v>0.04024632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.04048268</v>
+        <v>0.04049532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.6176</v>
+        <v>7.6274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>41364</v>
+        <v>41377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24.2016</v>
+        <v>24.1739</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.4396</v>
+        <v>4.3939</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47.1468</v>
+        <v>47.1348</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4762</v>
+        <v>0.4729</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.5238</v>
+        <v>0.5271</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2565,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
         <v>354</v>
@@ -2574,13 +2574,13 @@
         <v>951</v>
       </c>
       <c r="O3" t="n">
-        <v>4644.1101</v>
+        <v>4691.2522</v>
       </c>
       <c r="P3" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.7652</v>
+        <v>22.6631</v>
       </c>
       <c r="R3" t="n">
         <v>151.2965</v>
@@ -2604,7 +2604,7 @@
         <v>0.05370757</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.6438</v>
+        <v>4.6267</v>
       </c>
       <c r="Z3" t="n">
         <v>274</v>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
         <v>238</v>
@@ -2806,7 +2806,7 @@
         <v>0.04516027</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4318</v>
+        <v>2.1477</v>
       </c>
       <c r="Z5" t="n">
         <v>147</v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
         <v>347</v>
@@ -2877,13 +2877,13 @@
         <v>1047</v>
       </c>
       <c r="O6" t="n">
-        <v>5504.2737</v>
+        <v>5499.2737</v>
       </c>
       <c r="P6" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.2845</v>
+        <v>22.3548</v>
       </c>
       <c r="R6" t="n">
         <v>223.8234</v>
@@ -2907,7 +2907,7 @@
         <v>0.04464248</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.6807</v>
+        <v>3.5742</v>
       </c>
       <c r="Z6" t="n">
         <v>286</v>
@@ -2969,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
         <v>353</v>
@@ -3008,7 +3008,7 @@
         <v>0.05287085</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.1226</v>
+        <v>3.5376</v>
       </c>
       <c r="Z7" t="n">
         <v>310</v>
@@ -3070,22 +3070,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
         <v>337</v>
       </c>
       <c r="N8" t="n">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="O8" t="n">
-        <v>2914.0033</v>
+        <v>2942.9739</v>
       </c>
       <c r="P8" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q8" t="n">
-        <v>22.4154</v>
+        <v>22.4654</v>
       </c>
       <c r="R8" t="n">
         <v>254.9361</v>
@@ -3106,22 +3106,22 @@
         <v>0.0343527</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04303363</v>
+        <v>0.04299272</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.569</v>
+        <v>3.138</v>
       </c>
       <c r="Z8" t="n">
         <v>248</v>
       </c>
       <c r="AA8" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AB8" t="n">
-        <v>380.463</v>
+        <v>379.463</v>
       </c>
       <c r="AC8" t="n">
-        <v>1188.9747</v>
+        <v>1187.9747</v>
       </c>
       <c r="AD8" t="n">
         <v>7</v>
@@ -3133,7 +3133,7 @@
         <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.3621</v>
+        <v>6.521</v>
       </c>
     </row>
     <row r="9">
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
         <v>274</v>
@@ -3180,13 +3180,13 @@
         <v>875</v>
       </c>
       <c r="O9" t="n">
-        <v>2192.3221</v>
+        <v>2471.8734</v>
       </c>
       <c r="P9" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.1991</v>
+        <v>25.2232</v>
       </c>
       <c r="R9" t="n">
         <v>278.5929</v>
@@ -3210,7 +3210,7 @@
         <v>0.03314017</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.0768</v>
+        <v>1.4358</v>
       </c>
       <c r="Z9" t="n">
         <v>228</v>
@@ -3272,22 +3272,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N10" t="n">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="O10" t="n">
-        <v>1612.1951</v>
+        <v>1685.5504</v>
       </c>
       <c r="P10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.4188</v>
+        <v>31.2139</v>
       </c>
       <c r="R10" t="n">
         <v>195.7229</v>
@@ -3305,25 +3305,25 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02845478</v>
+        <v>0.02870221</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03432137</v>
+        <v>0.03441314</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5328</v>
+        <v>2.5546</v>
       </c>
       <c r="Z10" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AA10" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AB10" t="n">
-        <v>260.6518</v>
+        <v>263.066</v>
       </c>
       <c r="AC10" t="n">
-        <v>856.8377</v>
+        <v>859.2519</v>
       </c>
       <c r="AD10" t="n">
         <v>4</v>
@@ -3335,7 +3335,7 @@
         <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.815</v>
+        <v>7.0377</v>
       </c>
     </row>
     <row r="11">
@@ -3373,22 +3373,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="N11" t="n">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="O11" t="n">
-        <v>535.1442</v>
+        <v>669.9848</v>
       </c>
       <c r="P11" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.4791</v>
+        <v>31.904</v>
       </c>
       <c r="R11" t="n">
         <v>184.9949</v>
@@ -3406,37 +3406,37 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03050415</v>
+        <v>0.03114231</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03257451</v>
+        <v>0.03299695</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.0811</v>
+        <v>3.2433</v>
       </c>
       <c r="Z11" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AA11" t="n">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="AB11" t="n">
-        <v>263.7523</v>
+        <v>270.5807</v>
       </c>
       <c r="AC11" t="n">
-        <v>778.7128</v>
+        <v>788.5412</v>
       </c>
       <c r="AD11" t="n">
         <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
         <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>5.9049</v>
+        <v>6.6364</v>
       </c>
     </row>
     <row r="12">
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M12" t="n">
         <v>416</v>
@@ -3483,13 +3483,13 @@
         <v>1196</v>
       </c>
       <c r="O12" t="n">
-        <v>5595.2442</v>
+        <v>5315.6929</v>
       </c>
       <c r="P12" t="n">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.2747</v>
+        <v>21.094</v>
       </c>
       <c r="R12" t="n">
         <v>301.8061</v>
@@ -3513,7 +3513,7 @@
         <v>0.04349407</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.6507</v>
+        <v>3.6447</v>
       </c>
       <c r="Z12" t="n">
         <v>330</v>

--- a/results/543_z13/5_quantification/543_z13_quantification.xlsx
+++ b/results/543_z13/5_quantification/543_z13_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.3636</v>
+        <v>7.4545</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2923</v>
+        <v>2.7336</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>311</v>
+        <v>351.1818</v>
       </c>
       <c r="D13" t="n">
-        <v>331</v>
+        <v>368</v>
       </c>
       <c r="E13" t="n">
-        <v>58.9016</v>
+        <v>62.7404</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>923.7273</v>
+        <v>971.6364</v>
       </c>
       <c r="D14" t="n">
-        <v>912</v>
+        <v>1007</v>
       </c>
       <c r="E14" t="n">
-        <v>139.5049</v>
+        <v>137.5546</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2910.1134</v>
+        <v>3223.7739</v>
       </c>
       <c r="D15" t="n">
-        <v>2471.8734</v>
+        <v>3196.4247</v>
       </c>
       <c r="E15" t="n">
-        <v>1677.5872</v>
+        <v>1466.0703</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>127.4545</v>
+        <v>141.8182</v>
       </c>
       <c r="D16" t="n">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="E16" t="n">
-        <v>81.1669</v>
+        <v>70.4469</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.4052</v>
+        <v>23.7241</v>
       </c>
       <c r="D17" t="n">
-        <v>22.6631</v>
+        <v>22.5672</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8624</v>
+        <v>3.4393</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03751996</v>
+        <v>0.04236469</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03534304</v>
+        <v>0.03751274</v>
       </c>
       <c r="E23" t="n">
-        <v>0.008522099999999999</v>
+        <v>0.0096717</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04250902</v>
+        <v>0.04466928</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04349407</v>
+        <v>0.04430173</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00703491</v>
+        <v>0.00690422</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.113</v>
+        <v>3.6357</v>
       </c>
       <c r="D25" t="n">
-        <v>3.2433</v>
+        <v>3.5742</v>
       </c>
       <c r="E25" t="n">
-        <v>0.901</v>
+        <v>1.2776</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>245.5455</v>
+        <v>308.4545</v>
       </c>
       <c r="D26" t="n">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c r="E26" t="n">
-        <v>60.0889</v>
+        <v>77.867</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>658.8182</v>
+        <v>771.1818</v>
       </c>
       <c r="D27" t="n">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="E27" t="n">
-        <v>201.9613</v>
+        <v>237.2677</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>352.9911</v>
+        <v>398.4307</v>
       </c>
       <c r="D28" t="n">
-        <v>376.5341</v>
+        <v>419.5046</v>
       </c>
       <c r="E28" t="n">
-        <v>65.16759999999999</v>
+        <v>69.0766</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1047.5094</v>
+        <v>1099.8699</v>
       </c>
       <c r="D29" t="n">
-        <v>1055.0092</v>
+        <v>1126.9798</v>
       </c>
       <c r="E29" t="n">
-        <v>156.4744</v>
+        <v>155.7896</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.8182</v>
+        <v>8.545500000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>2.2724</v>
+        <v>2.0671</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11.0909</v>
+        <v>11.7273</v>
       </c>
       <c r="D31" t="n">
         <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>2.5477</v>
+        <v>2.4121</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.4545</v>
+        <v>13.3636</v>
       </c>
       <c r="D32" t="n">
         <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>2.1616</v>
+        <v>2.7303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.1679</v>
+        <v>7.3107</v>
       </c>
       <c r="D33" t="n">
-        <v>7.3794</v>
+        <v>7.4604</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5203</v>
+        <v>0.4988</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41377</v>
+        <v>43175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04024632</v>
+        <v>0.04199519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>926</v>
+        <v>992</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0009007</v>
+        <v>0.00096489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>179.1212</v>
+        <v>202.6995</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.045718</v>
+        <v>0.04769718</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.04024632</v>
+        <v>0.04199519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.04024632</v>
+        <v>0.04199519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.04049532</v>
+        <v>0.04224419</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.6274</v>
+        <v>7.7697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>41377</v>
+        <v>43175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>571</v>
+        <v>691</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24.1739</v>
+        <v>23.1285</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.3939</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47.1348</v>
+        <v>46.0563</v>
       </c>
     </row>
     <row r="12">
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.0487</v>
+        <v>50.0449</v>
       </c>
     </row>
     <row r="13">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4729</v>
+        <v>0.4515</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.5271</v>
+        <v>0.5485</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -2464,22 +2464,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="N2" t="n">
-        <v>912</v>
+        <v>833</v>
       </c>
       <c r="O2" t="n">
-        <v>3742.8187</v>
+        <v>3573.51</v>
       </c>
       <c r="P2" t="n">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.7606</v>
+        <v>21.3983</v>
       </c>
       <c r="R2" t="n">
         <v>205.0366</v>
@@ -2497,25 +2497,25 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03470997</v>
+        <v>0.03388634</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04047936</v>
+        <v>0.03697292</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4386</v>
+        <v>1.9509</v>
       </c>
       <c r="Z2" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AA2" t="n">
-        <v>826</v>
+        <v>658</v>
       </c>
       <c r="AB2" t="n">
-        <v>353.8894</v>
+        <v>343.0904</v>
       </c>
       <c r="AC2" t="n">
-        <v>1057.0458</v>
+        <v>961.6488000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>9</v>
@@ -2524,10 +2524,10 @@
         <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.4007</v>
+        <v>7.513</v>
       </c>
     </row>
     <row r="3">
@@ -2565,22 +2565,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>354</v>
+        <v>407</v>
       </c>
       <c r="N3" t="n">
-        <v>951</v>
+        <v>1013</v>
       </c>
       <c r="O3" t="n">
-        <v>4691.2522</v>
+        <v>4964.6786</v>
       </c>
       <c r="P3" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.6631</v>
+        <v>22.9846</v>
       </c>
       <c r="R3" t="n">
         <v>151.2965</v>
@@ -2598,37 +2598,37 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0507018</v>
+        <v>0.05829275</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05370757</v>
+        <v>0.05720901</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6267</v>
+        <v>6.6095</v>
       </c>
       <c r="Z3" t="n">
-        <v>274</v>
+        <v>397</v>
       </c>
       <c r="AA3" t="n">
-        <v>740</v>
+        <v>898</v>
       </c>
       <c r="AB3" t="n">
-        <v>391.2792</v>
+        <v>450.5929</v>
       </c>
       <c r="AC3" t="n">
-        <v>1062.2813</v>
+        <v>1127.3524</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AE3" t="n">
         <v>13</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.6482</v>
+        <v>7.046</v>
       </c>
     </row>
     <row r="4">
@@ -2666,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
-        <v>331</v>
+        <v>379</v>
       </c>
       <c r="N4" t="n">
-        <v>876</v>
+        <v>858</v>
       </c>
       <c r="O4" t="n">
-        <v>1524.5971</v>
+        <v>2549.4175</v>
       </c>
       <c r="P4" t="n">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.5903</v>
+        <v>21.7899</v>
       </c>
       <c r="R4" t="n">
         <v>205.0366</v>
@@ -2699,37 +2699,37 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04027254</v>
+        <v>0.04611267</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04370167</v>
+        <v>0.04280369</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.9017</v>
+        <v>4.3895</v>
       </c>
       <c r="Z4" t="n">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="AA4" t="n">
-        <v>523</v>
+        <v>678</v>
       </c>
       <c r="AB4" t="n">
-        <v>376.5341</v>
+        <v>434.5046</v>
       </c>
       <c r="AC4" t="n">
-        <v>993.7494</v>
+        <v>973.7788</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.4844</v>
+        <v>6.9607</v>
       </c>
     </row>
     <row r="5">
@@ -2770,19 +2770,19 @@
         <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="N5" t="n">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="O5" t="n">
-        <v>1293.3006</v>
+        <v>1309.3717</v>
       </c>
       <c r="P5" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.8712</v>
+        <v>23.3816</v>
       </c>
       <c r="R5" t="n">
         <v>139.6812</v>
@@ -2800,25 +2800,25 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03534304</v>
+        <v>0.03712504</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04516027</v>
+        <v>0.04579188</v>
       </c>
       <c r="Y5" t="n">
         <v>2.1477</v>
       </c>
       <c r="Z5" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="AA5" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="AB5" t="n">
-        <v>276.1076</v>
+        <v>289.7645</v>
       </c>
       <c r="AC5" t="n">
-        <v>972.1514</v>
+        <v>985.8082000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>4</v>
@@ -2830,7 +2830,7 @@
         <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.7768</v>
+        <v>7.7258</v>
       </c>
     </row>
     <row r="6">
@@ -2871,19 +2871,19 @@
         <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="N6" t="n">
-        <v>1047</v>
+        <v>1094</v>
       </c>
       <c r="O6" t="n">
-        <v>5499.2737</v>
+        <v>5461.2615</v>
       </c>
       <c r="P6" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.3548</v>
+        <v>22.5672</v>
       </c>
       <c r="R6" t="n">
         <v>223.8234</v>
@@ -2901,28 +2901,28 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03898876</v>
+        <v>0.04089888</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04464248</v>
+        <v>0.04664648</v>
       </c>
       <c r="Y6" t="n">
         <v>3.5742</v>
       </c>
       <c r="Z6" t="n">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="AA6" t="n">
-        <v>784</v>
+        <v>903</v>
       </c>
       <c r="AB6" t="n">
-        <v>389.3209</v>
+        <v>406.0782</v>
       </c>
       <c r="AC6" t="n">
-        <v>1168.3646</v>
+        <v>1215.9504</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -2931,7 +2931,7 @@
         <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.8264</v>
+        <v>7.9626</v>
       </c>
     </row>
     <row r="7">
@@ -2969,22 +2969,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="N7" t="n">
-        <v>942</v>
+        <v>1007</v>
       </c>
       <c r="O7" t="n">
-        <v>2173.9302</v>
+        <v>2678.7069</v>
       </c>
       <c r="P7" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.3171</v>
+        <v>20.2932</v>
       </c>
       <c r="R7" t="n">
         <v>141.3381</v>
@@ -3002,37 +3002,37 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05417434</v>
+        <v>0.06292204</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05287085</v>
+        <v>0.05651905</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.5376</v>
+        <v>4.2451</v>
       </c>
       <c r="Z7" t="n">
-        <v>310</v>
+        <v>377</v>
       </c>
       <c r="AA7" t="n">
-        <v>760</v>
+        <v>846</v>
       </c>
       <c r="AB7" t="n">
-        <v>392.5219</v>
+        <v>454.2498</v>
       </c>
       <c r="AC7" t="n">
-        <v>1055.0092</v>
+        <v>1126.9798</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
         <v>13</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.3794</v>
+        <v>7.4604</v>
       </c>
     </row>
     <row r="8">
@@ -3070,22 +3070,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="N8" t="n">
-        <v>1051</v>
+        <v>1083</v>
       </c>
       <c r="O8" t="n">
-        <v>2942.9739</v>
+        <v>3196.4247</v>
       </c>
       <c r="P8" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="Q8" t="n">
-        <v>22.4654</v>
+        <v>22.1974</v>
       </c>
       <c r="R8" t="n">
         <v>254.9361</v>
@@ -3103,28 +3103,28 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0343527</v>
+        <v>0.03751274</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04299272</v>
+        <v>0.04430173</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.138</v>
+        <v>3.5303</v>
       </c>
       <c r="Z8" t="n">
-        <v>248</v>
+        <v>336</v>
       </c>
       <c r="AA8" t="n">
-        <v>502</v>
+        <v>749</v>
       </c>
       <c r="AB8" t="n">
-        <v>379.463</v>
+        <v>419.5046</v>
       </c>
       <c r="AC8" t="n">
-        <v>1187.9747</v>
+        <v>1228.6022</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -3133,7 +3133,7 @@
         <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.521</v>
+        <v>6.5711</v>
       </c>
     </row>
     <row r="9">
@@ -3171,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>274</v>
+        <v>370</v>
       </c>
       <c r="N9" t="n">
-        <v>875</v>
+        <v>1037</v>
       </c>
       <c r="O9" t="n">
-        <v>2471.8734</v>
+        <v>3504.5933</v>
       </c>
       <c r="P9" t="n">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.2232</v>
+        <v>25.96</v>
       </c>
       <c r="R9" t="n">
         <v>278.5929</v>
@@ -3204,37 +3204,37 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02637913</v>
+        <v>0.03562145</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03314017</v>
+        <v>0.03927584</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4358</v>
+        <v>3.2305</v>
       </c>
       <c r="Z9" t="n">
-        <v>228</v>
+        <v>364</v>
       </c>
       <c r="AA9" t="n">
-        <v>855</v>
+        <v>1017</v>
       </c>
       <c r="AB9" t="n">
-        <v>315.9066</v>
+        <v>425.5046</v>
       </c>
       <c r="AC9" t="n">
-        <v>1017.4184</v>
+        <v>1199.4722</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.4497</v>
+        <v>7.5958</v>
       </c>
     </row>
     <row r="10">
@@ -3275,19 +3275,19 @@
         <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>232</v>
+        <v>289</v>
       </c>
       <c r="N10" t="n">
-        <v>750</v>
+        <v>878</v>
       </c>
       <c r="O10" t="n">
-        <v>1685.5504</v>
+        <v>2268.984</v>
       </c>
       <c r="P10" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="n">
-        <v>31.2139</v>
+        <v>28.3623</v>
       </c>
       <c r="R10" t="n">
         <v>195.7229</v>
@@ -3305,28 +3305,28 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02870221</v>
+        <v>0.03575405</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03441314</v>
+        <v>0.04028632</v>
       </c>
       <c r="Y10" t="n">
         <v>2.5546</v>
       </c>
       <c r="Z10" t="n">
-        <v>156</v>
+        <v>253</v>
       </c>
       <c r="AA10" t="n">
-        <v>498</v>
+        <v>704</v>
       </c>
       <c r="AB10" t="n">
-        <v>263.066</v>
+        <v>326.4508</v>
       </c>
       <c r="AC10" t="n">
-        <v>859.2519</v>
+        <v>998.1219</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>8</v>
@@ -3335,7 +3335,7 @@
         <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.0377</v>
+        <v>7.0944</v>
       </c>
     </row>
     <row r="11">
@@ -3373,22 +3373,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="N11" t="n">
-        <v>703</v>
+        <v>783</v>
       </c>
       <c r="O11" t="n">
-        <v>669.9848</v>
+        <v>1001.8499</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.904</v>
+        <v>31.3078</v>
       </c>
       <c r="R11" t="n">
         <v>184.9949</v>
@@ -3406,37 +3406,37 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03114231</v>
+        <v>0.0370134</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03299695</v>
+        <v>0.03675194</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.2433</v>
+        <v>3.7839</v>
       </c>
       <c r="Z11" t="n">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="AA11" t="n">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="AB11" t="n">
-        <v>270.5807</v>
+        <v>319.9655</v>
       </c>
       <c r="AC11" t="n">
-        <v>788.5412</v>
+        <v>876.2397</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF11" t="n">
         <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>6.6364</v>
+        <v>6.5541</v>
       </c>
     </row>
     <row r="12">
@@ -3474,22 +3474,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="N12" t="n">
-        <v>1196</v>
+        <v>1232</v>
       </c>
       <c r="O12" t="n">
-        <v>5315.6929</v>
+        <v>4952.7152</v>
       </c>
       <c r="P12" t="n">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.094</v>
+        <v>20.7227</v>
       </c>
       <c r="R12" t="n">
         <v>301.8061</v>
@@ -3507,37 +3507,37 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03795274</v>
+        <v>0.04087218</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04349407</v>
+        <v>0.04480326</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.6447</v>
+        <v>3.9761</v>
       </c>
       <c r="Z12" t="n">
-        <v>330</v>
+        <v>403</v>
       </c>
       <c r="AA12" t="n">
-        <v>966</v>
+        <v>1196</v>
       </c>
       <c r="AB12" t="n">
-        <v>474.2325</v>
+        <v>513.0315000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>1360.8154</v>
+        <v>1404.6144</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF12" t="n">
         <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.6863</v>
+        <v>7.9333</v>
       </c>
     </row>
   </sheetData>

--- a/results/543_z13/5_quantification/543_z13_quantification.xlsx
+++ b/results/543_z13/5_quantification/543_z13_quantification.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.4545</v>
+        <v>9.2727</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7336</v>
+        <v>3.3791</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>351.1818</v>
+        <v>377.1818</v>
       </c>
       <c r="D13" t="n">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="E13" t="n">
-        <v>62.7404</v>
+        <v>59.543</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>971.6364</v>
+        <v>1028.1818</v>
       </c>
       <c r="D14" t="n">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="E14" t="n">
-        <v>137.5546</v>
+        <v>131.7064</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3223.7739</v>
+        <v>3494.1416</v>
       </c>
       <c r="D15" t="n">
-        <v>3196.4247</v>
+        <v>3322.1841</v>
       </c>
       <c r="E15" t="n">
-        <v>1466.0703</v>
+        <v>1358.7337</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>141.8182</v>
+        <v>158.7273</v>
       </c>
       <c r="D16" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E16" t="n">
-        <v>70.4469</v>
+        <v>63.3642</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.7241</v>
+        <v>22.2109</v>
       </c>
       <c r="D17" t="n">
-        <v>22.5672</v>
+        <v>21.9425</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4393</v>
+        <v>2.262</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.04236469</v>
+        <v>0.04528973</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03751274</v>
+        <v>0.04404494</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0096717</v>
+        <v>0.007821089999999999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04466928</v>
+        <v>0.04719016</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04430173</v>
+        <v>0.04786059</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00690422</v>
+        <v>0.00578824</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.6357</v>
+        <v>4.4972</v>
       </c>
       <c r="D25" t="n">
-        <v>3.5742</v>
+        <v>4.0874</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2776</v>
+        <v>1.483</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>308.4545</v>
+        <v>337.5455</v>
       </c>
       <c r="D26" t="n">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="E26" t="n">
-        <v>77.867</v>
+        <v>77.0485</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>771.1818</v>
+        <v>825.8182</v>
       </c>
       <c r="D27" t="n">
-        <v>749</v>
+        <v>804</v>
       </c>
       <c r="E27" t="n">
-        <v>237.2677</v>
+        <v>207.3335</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>398.4307</v>
+        <v>427.512</v>
       </c>
       <c r="D28" t="n">
-        <v>419.5046</v>
+        <v>435.3209</v>
       </c>
       <c r="E28" t="n">
-        <v>69.0766</v>
+        <v>65.47629999999999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1099.8699</v>
+        <v>1164.1805</v>
       </c>
       <c r="D29" t="n">
-        <v>1126.9798</v>
+        <v>1126.7666</v>
       </c>
       <c r="E29" t="n">
-        <v>155.7896</v>
+        <v>149.8066</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8.545500000000001</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
         <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0671</v>
+        <v>2.6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11.7273</v>
+        <v>12.6364</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E31" t="n">
-        <v>2.4121</v>
+        <v>2.4196</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.3636</v>
+        <v>13.8182</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E32" t="n">
-        <v>2.7303</v>
+        <v>2.316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1299,29 +1299,87 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.1818</v>
+      </c>
+      <c r="D33" t="n">
+        <v>14</v>
+      </c>
+      <c r="E33" t="n">
+        <v>10.4768</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.4033</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>7.3107</v>
-      </c>
-      <c r="D33" t="n">
-        <v>7.4604</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.4988</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="C35" t="n">
+        <v>7.3801</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.379</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5054</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="G35" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1336,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1451,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>43175</v>
+        <v>44246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1471,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04199519</v>
+        <v>0.04303692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1491,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>992</v>
+        <v>1062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1511,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00096489</v>
+        <v>0.00103298</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1571,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1591,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>202.6995</v>
+        <v>217.9606</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1611,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1631,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04769718</v>
+        <v>0.04889348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1651,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.04199519</v>
+        <v>0.04303692</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1728,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.04199519</v>
+        <v>0.04303692</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,11 +1748,71 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.04224419</v>
+        <v>0.04328593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>231</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2192</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1864,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.7697</v>
+        <v>7.7853</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1944,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>43175</v>
+        <v>44246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +2087,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>691</v>
+        <v>739</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +2102,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.1285</v>
+        <v>21.5424</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +2117,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.47</v>
+        <v>3.784</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2132,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46.0563</v>
+        <v>43.6846</v>
       </c>
     </row>
     <row r="12">
@@ -2029,7 +2147,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.0449</v>
+        <v>50.0379</v>
       </c>
     </row>
     <row r="13">
@@ -2044,7 +2162,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4515</v>
+        <v>0.4195</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2177,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.5485</v>
+        <v>0.5805</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -2136,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -2259,7 +2377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,6 +2546,16 @@
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2464,22 +2592,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="N2" t="n">
-        <v>833</v>
+        <v>846</v>
       </c>
       <c r="O2" t="n">
-        <v>3573.51</v>
+        <v>3538.9953</v>
       </c>
       <c r="P2" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.3983</v>
+        <v>21.7116</v>
       </c>
       <c r="R2" t="n">
         <v>205.0366</v>
@@ -2497,37 +2625,43 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03388634</v>
+        <v>0.03506295</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03697292</v>
+        <v>0.03754993</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.9509</v>
+        <v>2.4386</v>
       </c>
       <c r="Z2" t="n">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="AA2" t="n">
-        <v>658</v>
+        <v>673</v>
       </c>
       <c r="AB2" t="n">
-        <v>343.0904</v>
+        <v>353.5046</v>
       </c>
       <c r="AC2" t="n">
-        <v>961.6488000000001</v>
+        <v>975.4773</v>
       </c>
       <c r="AD2" t="n">
         <v>9</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.513</v>
+        <v>7.5162</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.3865</v>
       </c>
     </row>
     <row r="3">
@@ -2565,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>407</v>
@@ -2574,13 +2708,13 @@
         <v>1013</v>
       </c>
       <c r="O3" t="n">
-        <v>4964.6786</v>
+        <v>5340.899</v>
       </c>
       <c r="P3" t="n">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.9846</v>
+        <v>22.5354</v>
       </c>
       <c r="R3" t="n">
         <v>151.2965</v>
@@ -2604,7 +2738,7 @@
         <v>0.05720901</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.6095</v>
+        <v>7.2705</v>
       </c>
       <c r="Z3" t="n">
         <v>397</v>
@@ -2613,10 +2747,10 @@
         <v>898</v>
       </c>
       <c r="AB3" t="n">
-        <v>450.5929</v>
+        <v>450.0071</v>
       </c>
       <c r="AC3" t="n">
-        <v>1127.3524</v>
+        <v>1126.7666</v>
       </c>
       <c r="AD3" t="n">
         <v>9</v>
@@ -2628,7 +2762,13 @@
         <v>15</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.046</v>
+        <v>7.1326</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.5865</v>
       </c>
     </row>
     <row r="4">
@@ -2666,22 +2806,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M4" t="n">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="N4" t="n">
-        <v>858</v>
+        <v>923</v>
       </c>
       <c r="O4" t="n">
-        <v>2549.4175</v>
+        <v>1906.6753</v>
       </c>
       <c r="P4" t="n">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.7899</v>
+        <v>23.2521</v>
       </c>
       <c r="R4" t="n">
         <v>205.0366</v>
@@ -2699,37 +2839,43 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04611267</v>
+        <v>0.04526098</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04280369</v>
+        <v>0.0460464</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.3895</v>
+        <v>6.3403</v>
       </c>
       <c r="Z4" t="n">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="AA4" t="n">
-        <v>678</v>
+        <v>601</v>
       </c>
       <c r="AB4" t="n">
-        <v>434.5046</v>
+        <v>422.5046</v>
       </c>
       <c r="AC4" t="n">
-        <v>973.7788</v>
+        <v>1045.1341</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
       </c>
       <c r="AF4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.9607</v>
+        <v>6.7416</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.3537</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2913,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="N5" t="n">
-        <v>870</v>
+        <v>919</v>
       </c>
       <c r="O5" t="n">
-        <v>1309.3717</v>
+        <v>2095.2561</v>
       </c>
       <c r="P5" t="n">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="Q5" t="n">
-        <v>23.3816</v>
+        <v>18.7076</v>
       </c>
       <c r="R5" t="n">
         <v>139.6812</v>
@@ -2800,37 +2946,43 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03712504</v>
+        <v>0.04098604</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04579188</v>
+        <v>0.04837097</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.1477</v>
+        <v>2.8637</v>
       </c>
       <c r="Z5" t="n">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="AA5" t="n">
-        <v>470</v>
+        <v>512</v>
       </c>
       <c r="AB5" t="n">
-        <v>289.7645</v>
+        <v>317.8356</v>
       </c>
       <c r="AC5" t="n">
-        <v>985.8082000000001</v>
+        <v>1037.6367</v>
       </c>
       <c r="AD5" t="n">
         <v>4</v>
       </c>
       <c r="AE5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.7258</v>
+        <v>7.9621</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.4286</v>
       </c>
     </row>
     <row r="6">
@@ -2868,22 +3020,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="N6" t="n">
-        <v>1094</v>
+        <v>1124</v>
       </c>
       <c r="O6" t="n">
-        <v>5461.2615</v>
+        <v>5814.7711</v>
       </c>
       <c r="P6" t="n">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.5672</v>
+        <v>21.9425</v>
       </c>
       <c r="R6" t="n">
         <v>223.8234</v>
@@ -2901,37 +3053,43 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04089888</v>
+        <v>0.04404494</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04664648</v>
+        <v>0.04792564</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.5742</v>
+        <v>4.4678</v>
       </c>
       <c r="Z6" t="n">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="AA6" t="n">
-        <v>903</v>
+        <v>928</v>
       </c>
       <c r="AB6" t="n">
-        <v>406.0782</v>
+        <v>435.3209</v>
       </c>
       <c r="AC6" t="n">
-        <v>1215.9504</v>
+        <v>1248.7788</v>
       </c>
       <c r="AD6" t="n">
         <v>9</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.9626</v>
+        <v>7.7742</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>31</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.4679</v>
       </c>
     </row>
     <row r="7">
@@ -2969,22 +3127,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="N7" t="n">
-        <v>1007</v>
+        <v>989</v>
       </c>
       <c r="O7" t="n">
-        <v>2678.7069</v>
+        <v>2359.6408</v>
       </c>
       <c r="P7" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.2932</v>
+        <v>19.0294</v>
       </c>
       <c r="R7" t="n">
         <v>141.3381</v>
@@ -3002,37 +3160,43 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06292204</v>
+        <v>0.06077348</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05651905</v>
+        <v>0.05550878</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.2451</v>
+        <v>3.5376</v>
       </c>
       <c r="Z7" t="n">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="AA7" t="n">
-        <v>846</v>
+        <v>804</v>
       </c>
       <c r="AB7" t="n">
-        <v>454.2498</v>
+        <v>442.4924</v>
       </c>
       <c r="AC7" t="n">
-        <v>1126.9798</v>
+        <v>1108.9798</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
         <v>13</v>
       </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.4604</v>
+        <v>7.3783</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.3306</v>
       </c>
     </row>
     <row r="8">
@@ -3070,22 +3234,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>368</v>
+        <v>441</v>
       </c>
       <c r="N8" t="n">
-        <v>1083</v>
+        <v>1170</v>
       </c>
       <c r="O8" t="n">
-        <v>3196.4247</v>
+        <v>4311.9314</v>
       </c>
       <c r="P8" t="n">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="Q8" t="n">
-        <v>22.1974</v>
+        <v>21.3462</v>
       </c>
       <c r="R8" t="n">
         <v>254.9361</v>
@@ -3103,37 +3267,43 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03751274</v>
+        <v>0.04495413</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04430173</v>
+        <v>0.04786059</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.5303</v>
+        <v>5.4916</v>
       </c>
       <c r="Z8" t="n">
-        <v>336</v>
+        <v>418</v>
       </c>
       <c r="AA8" t="n">
-        <v>749</v>
+        <v>914</v>
       </c>
       <c r="AB8" t="n">
-        <v>419.5046</v>
+        <v>501.3747</v>
       </c>
       <c r="AC8" t="n">
-        <v>1228.6022</v>
+        <v>1329.9575</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF8" t="n">
         <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.5711</v>
+        <v>6.6814</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.505</v>
       </c>
     </row>
     <row r="9">
@@ -3171,22 +3341,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="N9" t="n">
-        <v>1037</v>
+        <v>1080</v>
       </c>
       <c r="O9" t="n">
-        <v>3504.5933</v>
+        <v>3322.1841</v>
       </c>
       <c r="P9" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.96</v>
+        <v>25.1681</v>
       </c>
       <c r="R9" t="n">
         <v>278.5929</v>
@@ -3204,37 +3374,43 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03562145</v>
+        <v>0.0387985</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03927584</v>
+        <v>0.04090444</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.2305</v>
+        <v>3.5895</v>
       </c>
       <c r="Z9" t="n">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="AA9" t="n">
-        <v>1017</v>
+        <v>1055</v>
       </c>
       <c r="AB9" t="n">
-        <v>425.5046</v>
+        <v>462.8183</v>
       </c>
       <c r="AC9" t="n">
-        <v>1199.4722</v>
+        <v>1243.7859</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF9" t="n">
         <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.5958</v>
+        <v>7.8306</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.3182</v>
       </c>
     </row>
     <row r="10">
@@ -3272,22 +3448,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>289</v>
+        <v>322</v>
       </c>
       <c r="N10" t="n">
-        <v>878</v>
+        <v>915</v>
       </c>
       <c r="O10" t="n">
-        <v>2268.984</v>
+        <v>2315.5403</v>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="Q10" t="n">
-        <v>28.3623</v>
+        <v>25.4455</v>
       </c>
       <c r="R10" t="n">
         <v>195.7229</v>
@@ -3305,25 +3481,25 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03575405</v>
+        <v>0.03983669</v>
       </c>
       <c r="X10" t="n">
-        <v>0.04028632</v>
+        <v>0.04198403</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5546</v>
+        <v>4.0874</v>
       </c>
       <c r="Z10" t="n">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="AA10" t="n">
-        <v>704</v>
+        <v>738</v>
       </c>
       <c r="AB10" t="n">
-        <v>326.4508</v>
+        <v>361.9361</v>
       </c>
       <c r="AC10" t="n">
-        <v>998.1219</v>
+        <v>1042.2641</v>
       </c>
       <c r="AD10" t="n">
         <v>8</v>
@@ -3332,10 +3508,16 @@
         <v>8</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.0944</v>
+        <v>7.379</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.3407</v>
       </c>
     </row>
     <row r="11">
@@ -3373,22 +3555,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>290</v>
+        <v>367</v>
       </c>
       <c r="N11" t="n">
-        <v>783</v>
+        <v>1037</v>
       </c>
       <c r="O11" t="n">
-        <v>1001.8499</v>
+        <v>2788.8612</v>
       </c>
       <c r="P11" t="n">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.3078</v>
+        <v>24.4637</v>
       </c>
       <c r="R11" t="n">
         <v>184.9949</v>
@@ -3406,37 +3588,43 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0370134</v>
+        <v>0.0468411</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03675194</v>
+        <v>0.04867402</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.7839</v>
+        <v>5.4056</v>
       </c>
       <c r="Z11" t="n">
-        <v>221</v>
+        <v>300</v>
       </c>
       <c r="AA11" t="n">
-        <v>364</v>
+        <v>730</v>
       </c>
       <c r="AB11" t="n">
-        <v>319.9655</v>
+        <v>411.9777</v>
       </c>
       <c r="AC11" t="n">
-        <v>876.2397</v>
+        <v>1169.4773</v>
       </c>
       <c r="AD11" t="n">
         <v>7</v>
       </c>
       <c r="AE11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>6.5541</v>
+        <v>6.7286</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.2719</v>
       </c>
     </row>
     <row r="12">
@@ -3477,19 +3665,19 @@
         <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="N12" t="n">
-        <v>1232</v>
+        <v>1294</v>
       </c>
       <c r="O12" t="n">
-        <v>4952.7152</v>
+        <v>4640.8035</v>
       </c>
       <c r="P12" t="n">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="Q12" t="n">
-        <v>20.7227</v>
+        <v>20.7179</v>
       </c>
       <c r="R12" t="n">
         <v>301.8061</v>
@@ -3507,37 +3695,43 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04087218</v>
+        <v>0.04333546</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04480326</v>
+        <v>0.04705797</v>
       </c>
       <c r="Y12" t="n">
         <v>3.9761</v>
       </c>
       <c r="Z12" t="n">
-        <v>403</v>
+        <v>451</v>
       </c>
       <c r="AA12" t="n">
-        <v>1196</v>
+        <v>1231</v>
       </c>
       <c r="AB12" t="n">
-        <v>513.0315000000001</v>
+        <v>542.86</v>
       </c>
       <c r="AC12" t="n">
-        <v>1404.6144</v>
+        <v>1477.7271</v>
       </c>
       <c r="AD12" t="n">
         <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF12" t="n">
         <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.9333</v>
+        <v>8.0565</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.4464</v>
       </c>
     </row>
   </sheetData>
